--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536135_LIGAREGULARA_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536135_LIGAREGULARA_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ GONZÁLEZ</t>
+          <t>J. PLEASANT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.215</v>
+        <v>-1.1331</v>
       </c>
       <c r="E18" t="n">
-        <v>1.215</v>
+        <v>-2.2844</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1.1513</v>
       </c>
       <c r="G18" t="n">
-        <v>1.215</v>
+        <v>-1.4026</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-0.2944</v>
       </c>
       <c r="I18" t="n">
-        <v>1.215</v>
+        <v>-1.1081</v>
       </c>
       <c r="J18" t="n">
-        <v>1.215</v>
+        <v>-1.4745</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-0.3565</v>
       </c>
       <c r="L18" t="n">
-        <v>1.215</v>
+        <v>-1.118</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1699</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.5599</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.1581</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0.202</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.2786</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PLEASANT</t>
+          <t>R. ISSANZA TSHUKA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1331</v>
+        <v>-2.5977</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2844</v>
+        <v>-2.0181</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1513</v>
+        <v>-0.5796</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4026</v>
+        <v>-0.6641</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2944</v>
+        <v>-1.0644</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1081</v>
+        <v>0.4003</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.4745</v>
+        <v>-0.2555</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3565</v>
+        <v>-0.377</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.118</v>
+        <v>0.1215</v>
       </c>
       <c r="M19" t="n">
-        <v>0.07190000000000001</v>
+        <v>-0.4086</v>
       </c>
       <c r="N19" t="n">
-        <v>0.062</v>
+        <v>-0.6874</v>
       </c>
       <c r="O19" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.2788</v>
       </c>
       <c r="P19" t="n">
-        <v>0.39</v>
+        <v>-1.1699</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1699</v>
+        <v>-1.9499</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5599</v>
+        <v>0.7799</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1581</v>
+        <v>0.6475</v>
       </c>
       <c r="T19" t="n">
-        <v>0.36</v>
+        <v>0.1873</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.202</v>
+        <v>0.4602</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2786</v>
+        <v>-1.4112</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2786</v>
+        <v>-1.4112</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. ISSANZA TSHUKA</t>
+          <t>M. VARELA BARCIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5977</v>
+        <v>-3.9556</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0181</v>
+        <v>-3.4232</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5796</v>
+        <v>-0.5324</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6641</v>
+        <v>-4.8468</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0644</v>
+        <v>-2.8895</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4003</v>
+        <v>-1.9572</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2555</v>
+        <v>-3.9611</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.377</v>
+        <v>-2.0005</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1215</v>
+        <v>-1.9605</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4086</v>
+        <v>-0.8857</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6874</v>
+        <v>-0.889</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2788</v>
+        <v>0.0033</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1699</v>
+        <v>0.195</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9499</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7799</v>
+        <v>0.195</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6475</v>
+        <v>0.6962</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1873</v>
+        <v>0.5379</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4602</v>
+        <v>0.1583</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.4112</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4112</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. VARELA BARCIA</t>
+          <t>P. SANCHEZ INFANTES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9556</v>
+        <v>-5.1285</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4232</v>
+        <v>-6.5959</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5324</v>
+        <v>1.4674</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.8468</v>
+        <v>-1.4445</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.8895</v>
+        <v>-1.6065</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9572</v>
+        <v>0.162</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.9611</v>
+        <v>-1.2425</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.0005</v>
+        <v>-1.2585</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9605</v>
+        <v>0.016</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8857</v>
+        <v>-0.202</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.889</v>
+        <v>-0.348</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0033</v>
+        <v>0.146</v>
       </c>
       <c r="P21" t="n">
-        <v>0.195</v>
+        <v>-3.5097</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-4.8746</v>
       </c>
       <c r="R21" t="n">
-        <v>0.195</v>
+        <v>1.3649</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6962</v>
+        <v>0.0697</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5379</v>
+        <v>-0.4788</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1583</v>
+        <v>0.5485</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.244</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.244</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. SANCHEZ INFANTES</t>
+          <t>J. JIMENEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.1285</v>
+        <v>-7.2739</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.5959</v>
+        <v>-8.079499999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4674</v>
+        <v>0.8056</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4445</v>
+        <v>-5.1459</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6065</v>
+        <v>-2.6151</v>
       </c>
       <c r="I22" t="n">
-        <v>0.162</v>
+        <v>-2.5309</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2425</v>
+        <v>-5.7621</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2585</v>
+        <v>-2.5375</v>
       </c>
       <c r="L22" t="n">
-        <v>0.016</v>
+        <v>-3.2246</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.202</v>
+        <v>0.6162</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.348</v>
+        <v>-0.0775</v>
       </c>
       <c r="O22" t="n">
-        <v>0.146</v>
+        <v>0.6937</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.5097</v>
+        <v>-0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.8746</v>
+        <v>-2.1448</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3649</v>
+        <v>2.1448</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0697</v>
+        <v>-0.3854</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4788</v>
+        <v>-0.1726</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5485</v>
+        <v>-0.2128</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.244</v>
+        <v>-1.7426</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.244</v>
+        <v>-1.7426</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. JIMENEZ GONZALEZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,152 +2297,69 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.489000000000001</v>
+        <v>-0.6822000000000017</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.294499999999999</v>
+        <v>-6.113700000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8056</v>
+        <v>5.4314</v>
       </c>
       <c r="G23" t="n">
-        <v>-6.361</v>
+        <v>-2.485700000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.6151</v>
+        <v>-7.1668</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.7459</v>
+        <v>4.6813</v>
       </c>
       <c r="J23" t="n">
-        <v>-6.9771</v>
+        <v>0.895500000000002</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.5375</v>
+        <v>-1.6453</v>
       </c>
       <c r="L23" t="n">
-        <v>-4.4396</v>
+        <v>2.5408</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6162</v>
+        <v>-3.3812</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0775</v>
+        <v>-5.521599999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6937</v>
+        <v>2.1405</v>
       </c>
       <c r="P23" t="n">
-        <v>-0</v>
+        <v>0.9750999999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1448</v>
+        <v>-12.674</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1448</v>
+        <v>13.649</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3854</v>
+        <v>3.4943</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1726</v>
+        <v>2.4419</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2128</v>
+        <v>1.0522</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.7426</v>
+        <v>-2.6658</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.2229</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.7426</v>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>play_by_play_2536135_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>C.B. STARLABS MORÓN</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>-0.6823000000000023</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-6.113700000000001</v>
-      </c>
-      <c r="F24" t="n">
-        <v>5.4314</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-2.4858</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-7.1668</v>
-      </c>
-      <c r="I24" t="n">
-        <v>4.681300000000001</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.895500000000002</v>
-      </c>
-      <c r="K24" t="n">
-        <v>-1.645299999999999</v>
-      </c>
-      <c r="L24" t="n">
-        <v>2.540800000000001</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-3.3812</v>
-      </c>
-      <c r="N24" t="n">
-        <v>-5.521599999999999</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.1405</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0.9751000000000007</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>-12.674</v>
-      </c>
-      <c r="R24" t="n">
-        <v>13.649</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.4943</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.4419</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.0522</v>
-      </c>
-      <c r="V24" t="n">
-        <v>-2.6658</v>
-      </c>
-      <c r="W24" t="n">
-        <v>3.2229</v>
-      </c>
-      <c r="X24" t="n">
         <v>-5.8887</v>
       </c>
-      <c r="Y24" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
